--- a/2025_demo/GlycoMSP_MAS_template.xlsx
+++ b/2025_demo/GlycoMSP_MAS_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\其他電腦\My Computer\GlycoMSParser\2025_demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93BDB5F-33B3-4E61-8DBA-504683906D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160CBAE9-1E09-460F-AC76-4AD38DC9B791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{CFD31651-57D7-40EF-BE95-C7417EC3B9A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{CFD31651-57D7-40EF-BE95-C7417EC3B9A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Glycanlist" sheetId="2" r:id="rId1"/>
@@ -22,15 +22,16 @@
     <sheet name="conversion_log" sheetId="3" r:id="rId7"/>
     <sheet name="MS2_ref (DEMO)" sheetId="9" r:id="rId8"/>
     <sheet name="MAS_MLref (DEMO)" sheetId="10" r:id="rId9"/>
+    <sheet name="工作表1" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glycanlist!$A$1:$T$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ionlist!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MSlist!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MSlist!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="1" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="322">
   <si>
     <t>Glycan name/abbr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1049,10 +1050,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KDN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Neu5Ac</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1261,6 +1258,57 @@
   </si>
   <si>
     <t>(Full table saved in another file managed by GlycoMSP)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeX</t>
+  </si>
+  <si>
+    <t>fragmentation type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Gal(1-4)(Fuc(1-3)-GlcNAc) OR </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glycotope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glycotope (customizable)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fragementation mass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neu5Ac-Gal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neu5Ac-Gal-GlcNAc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SialylLacNac</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Structure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Composition</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4903,3259 +4951,3314 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBCDA65-1722-4232-88B5-A53E589EDED4}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="29.125" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820557B-6CE2-4FD8-86A4-E2CD52A6D2FD}">
-  <dimension ref="A1:J190"/>
+  <dimension ref="A1:K190"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="2" width="18.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
         <v>201</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>193</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>140</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>141</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>142</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>143</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>144</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>145</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>162</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>12636</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>162</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>12798</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>162</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>14353</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>162</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>14199</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>167</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>17172</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>167</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>16060</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>167</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>15485</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2</v>
       </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>167</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>16239</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>167</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>16204</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>167</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>15922</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>167</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>17720</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>2</v>
       </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>167</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>16094</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>2</v>
       </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>167</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>17537</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>2</v>
       </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>167</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>16424</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>2</v>
       </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>167</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>17353</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>2</v>
       </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>165</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>19126</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>2</v>
       </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>169</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>18562</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>3</v>
       </c>
-      <c r="E18" s="6">
-        <v>0</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>169</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>17392</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>2</v>
       </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="F19" s="6">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>169</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>17247</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>3</v>
       </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="F20" s="6">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>169</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>16833</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>2</v>
       </c>
-      <c r="E21" s="6">
-        <v>0</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>169</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>17205</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>2</v>
       </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="F22" s="6">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>169</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>18250</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>2</v>
       </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="F23" s="6">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>169</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>17021</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>3</v>
       </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="F24" s="6">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>169</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>17020</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>2</v>
       </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>169</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>18589</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>2</v>
       </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="F26" s="6">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>169</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>18431</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>2</v>
       </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>171</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>23988</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>2</v>
       </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>171</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>23871</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>2</v>
       </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>171</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>25242</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>2</v>
       </c>
-      <c r="E30" s="6">
-        <v>0</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>171</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>24039</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>3</v>
       </c>
-      <c r="E31" s="6">
-        <v>0</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>173</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>20605</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>2</v>
       </c>
-      <c r="E32" s="6">
-        <v>0</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="F32" s="6">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>173</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>20523</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>3</v>
       </c>
-      <c r="E33" s="6">
-        <v>0</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>173</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>19425</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>2</v>
       </c>
-      <c r="E34" s="6">
-        <v>0</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="F34" s="6">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>173</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>19348</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>3</v>
       </c>
-      <c r="E35" s="6">
-        <v>0</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>168</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>19314</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>2</v>
       </c>
-      <c r="E36" s="6">
-        <v>0</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="F36" s="6">
+        <v>0</v>
+      </c>
+      <c r="G36" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>168</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>21263</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>2</v>
       </c>
-      <c r="E37" s="6">
-        <v>0</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>168</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>20896</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>2</v>
       </c>
-      <c r="E38" s="6">
-        <v>0</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>168</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>19550</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>2</v>
       </c>
-      <c r="E39" s="6">
-        <v>0</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="F39" s="6">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>172</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>19313</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>2</v>
       </c>
-      <c r="E40" s="6">
-        <v>0</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="F40" s="6">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>172</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>18066</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>3</v>
       </c>
-      <c r="E41" s="6">
-        <v>0</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>172</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>17770</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>2</v>
       </c>
-      <c r="E42" s="6">
-        <v>0</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="F42" s="6">
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>172</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>19301</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>3</v>
       </c>
-      <c r="E43" s="6">
-        <v>0</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>172</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>19409</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>3</v>
       </c>
-      <c r="E44" s="6">
-        <v>0</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="F44" s="6">
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>172</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>19491</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>3</v>
       </c>
-      <c r="E45" s="6">
-        <v>0</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="F45" s="6">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>172</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>17954</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>2</v>
       </c>
-      <c r="E46" s="6">
-        <v>0</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="F46" s="6">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>172</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>17882</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>3</v>
       </c>
-      <c r="E47" s="6">
-        <v>0</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>170</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>19211</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>3</v>
       </c>
-      <c r="E48" s="6">
-        <v>0</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>170</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>19231</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>2</v>
       </c>
-      <c r="E49" s="6">
-        <v>0</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>179</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>31458</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>2</v>
       </c>
-      <c r="E50" s="6">
-        <v>0</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="F50" s="6">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>179</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>31272</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>3</v>
       </c>
-      <c r="E51" s="6">
-        <v>0</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>179</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>31457</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>3</v>
       </c>
-      <c r="E52" s="6">
-        <v>0</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="F52" s="6">
+        <v>0</v>
+      </c>
+      <c r="G52" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>179</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>30330</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>2</v>
       </c>
-      <c r="E53" s="6">
-        <v>0</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>179</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>30446</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>3</v>
       </c>
-      <c r="E54" s="6">
-        <v>0</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="F54" s="6">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>179</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>30292</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>3</v>
       </c>
-      <c r="E55" s="6">
-        <v>0</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="F55" s="6">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>175</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>19532</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>2</v>
       </c>
-      <c r="E56" s="6">
-        <v>0</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="F56" s="6">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>175</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>20719</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>3</v>
       </c>
-      <c r="E57" s="6">
-        <v>0</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="F57" s="6">
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>175</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>21037</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>2</v>
       </c>
-      <c r="E58" s="6">
-        <v>0</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="F58" s="6">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>175</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>21276</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>2</v>
       </c>
-      <c r="E59" s="6">
-        <v>0</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="F59" s="6">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>175</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>20899</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>3</v>
       </c>
-      <c r="E60" s="6">
-        <v>0</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="F60" s="6">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>175</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>20204</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>2</v>
       </c>
-      <c r="E61" s="6">
-        <v>0</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="F61" s="6">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>175</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>21345</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>3</v>
       </c>
-      <c r="E62" s="6">
-        <v>0</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="F62" s="6">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>175</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>20161</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>3</v>
       </c>
-      <c r="E63" s="6">
-        <v>0</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="F63" s="6">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>175</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>21144</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>3</v>
       </c>
-      <c r="E64" s="6">
-        <v>0</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="F64" s="6">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>175</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>21080</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>2</v>
       </c>
-      <c r="E65" s="6">
-        <v>0</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="F65" s="6">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>175</v>
       </c>
-      <c r="B66">
+      <c r="C66">
         <v>20021</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>2</v>
       </c>
-      <c r="E66" s="6">
-        <v>0</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="F66" s="6">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>175</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>19816</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>2</v>
       </c>
-      <c r="E67" s="6">
-        <v>0</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="F67" s="6">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>175</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>20008</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>3</v>
       </c>
-      <c r="E68" s="6">
-        <v>0</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="F68" s="6">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>175</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>19813</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>3</v>
       </c>
-      <c r="E69" s="6">
-        <v>0</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="F69" s="6">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>180</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>30609</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>3</v>
       </c>
-      <c r="E70" s="6">
-        <v>0</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="F70" s="6">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>180</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>30458</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>2</v>
       </c>
-      <c r="E71" s="6">
-        <v>0</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="F71" s="6">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>180</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>30411</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>2</v>
       </c>
-      <c r="E72" s="6">
-        <v>0</v>
-      </c>
-      <c r="F72" t="s">
+      <c r="F72" s="6">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>180</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>30333</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>2</v>
       </c>
-      <c r="E73" s="6">
-        <v>0</v>
-      </c>
-      <c r="F73" t="s">
+      <c r="F73" s="6">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>174</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>25410</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>3</v>
       </c>
-      <c r="E74" s="6">
-        <v>0</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="F74" s="6">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>174</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>25012</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>3</v>
       </c>
-      <c r="E75" s="6">
-        <v>0</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="F75" s="6">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>174</v>
       </c>
-      <c r="B76">
+      <c r="C76">
         <v>19376</v>
       </c>
-      <c r="D76">
+      <c r="E76">
         <v>2</v>
       </c>
-      <c r="E76" s="6">
-        <v>0</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="F76" s="6">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>174</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>25253</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>2</v>
       </c>
-      <c r="E77" s="6">
-        <v>0</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="F77" s="6">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>174</v>
       </c>
-      <c r="B78">
+      <c r="C78">
         <v>24797</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>2</v>
       </c>
-      <c r="E78" s="6">
-        <v>0</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="F78" s="6">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>174</v>
       </c>
-      <c r="B79">
+      <c r="C79">
         <v>26112</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>3</v>
       </c>
-      <c r="E79" s="6">
-        <v>0</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="F79" s="6">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>174</v>
       </c>
-      <c r="B80">
+      <c r="C80">
         <v>25865</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>3</v>
       </c>
-      <c r="E80" s="6">
-        <v>0</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="F80" s="6">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>174</v>
       </c>
-      <c r="B81">
+      <c r="C81">
         <v>18942</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>2</v>
       </c>
-      <c r="E81" s="6">
-        <v>0</v>
-      </c>
-      <c r="F81" t="s">
+      <c r="F81" s="6">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>174</v>
       </c>
-      <c r="B82">
+      <c r="C82">
         <v>18338</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>2</v>
       </c>
-      <c r="E82" s="6">
-        <v>0</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="F82" s="6">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>174</v>
       </c>
-      <c r="B83">
+      <c r="C83">
         <v>25769</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>2</v>
       </c>
-      <c r="E83" s="6">
-        <v>0</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="F83" s="6">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>174</v>
       </c>
-      <c r="B84">
+      <c r="C84">
         <v>25000</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>2</v>
       </c>
-      <c r="E84" s="6">
-        <v>0</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="F84" s="6">
+        <v>0</v>
+      </c>
+      <c r="G84" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>174</v>
       </c>
-      <c r="B85">
+      <c r="C85">
         <v>25965</v>
       </c>
-      <c r="D85">
+      <c r="E85">
         <v>2</v>
       </c>
-      <c r="E85" s="6">
-        <v>0</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="F85" s="6">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>174</v>
       </c>
-      <c r="B86">
+      <c r="C86">
         <v>18563</v>
       </c>
-      <c r="D86">
+      <c r="E86">
         <v>2</v>
       </c>
-      <c r="E86" s="6">
-        <v>0</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="F86" s="6">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>174</v>
       </c>
-      <c r="B87">
+      <c r="C87">
         <v>24766</v>
       </c>
-      <c r="D87">
+      <c r="E87">
         <v>3</v>
       </c>
-      <c r="E87" s="6">
-        <v>0</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="F87" s="6">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>174</v>
       </c>
-      <c r="B88">
+      <c r="C88">
         <v>18746</v>
       </c>
-      <c r="D88">
+      <c r="E88">
         <v>2</v>
       </c>
-      <c r="E88" s="6">
-        <v>0</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="F88" s="6">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>174</v>
       </c>
-      <c r="B89">
+      <c r="C89">
         <v>24637</v>
       </c>
-      <c r="D89">
+      <c r="E89">
         <v>2</v>
       </c>
-      <c r="E89" s="6">
-        <v>0</v>
-      </c>
-      <c r="F89" t="s">
+      <c r="F89" s="6">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>174</v>
       </c>
-      <c r="B90">
+      <c r="C90">
         <v>18612</v>
       </c>
-      <c r="D90">
+      <c r="E90">
         <v>3</v>
       </c>
-      <c r="E90" s="6">
-        <v>0</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="F90" s="6">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>174</v>
       </c>
-      <c r="B91">
+      <c r="C91">
         <v>25668</v>
       </c>
-      <c r="D91">
+      <c r="E91">
         <v>3</v>
       </c>
-      <c r="E91" s="6">
-        <v>0</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="F91" s="6">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>174</v>
       </c>
-      <c r="B92">
+      <c r="C92">
         <v>20035</v>
       </c>
-      <c r="D92">
+      <c r="E92">
         <v>3</v>
       </c>
-      <c r="E92" s="6">
-        <v>0</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="F92" s="6">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>181</v>
       </c>
-      <c r="B93">
+      <c r="C93">
         <v>21795</v>
       </c>
-      <c r="D93">
+      <c r="E93">
         <v>3</v>
       </c>
-      <c r="E93" s="6">
-        <v>0</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="F93" s="6">
+        <v>0</v>
+      </c>
+      <c r="G93" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>181</v>
       </c>
-      <c r="B94">
+      <c r="C94">
         <v>22173</v>
       </c>
-      <c r="D94">
+      <c r="E94">
         <v>2</v>
       </c>
-      <c r="E94" s="6">
-        <v>0</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="F94" s="6">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>181</v>
       </c>
-      <c r="B95">
+      <c r="C95">
         <v>20547</v>
       </c>
-      <c r="D95">
+      <c r="E95">
         <v>3</v>
       </c>
-      <c r="E95" s="6">
-        <v>0</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="F95" s="6">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>181</v>
       </c>
-      <c r="B96">
+      <c r="C96">
         <v>22298</v>
       </c>
-      <c r="D96">
+      <c r="E96">
         <v>3</v>
       </c>
-      <c r="E96" s="6">
-        <v>0</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="F96" s="6">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>181</v>
       </c>
-      <c r="B97">
+      <c r="C97">
         <v>21991</v>
       </c>
-      <c r="D97">
+      <c r="E97">
         <v>3</v>
       </c>
-      <c r="E97" s="6">
-        <v>0</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="F97" s="6">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>181</v>
       </c>
-      <c r="B98">
+      <c r="C98">
         <v>20818</v>
       </c>
-      <c r="D98">
+      <c r="E98">
         <v>3</v>
       </c>
-      <c r="E98" s="6">
-        <v>0</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="F98" s="6">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>181</v>
       </c>
-      <c r="B99">
+      <c r="C99">
         <v>21612</v>
       </c>
-      <c r="D99">
+      <c r="E99">
         <v>3</v>
       </c>
-      <c r="E99" s="6">
-        <v>0</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="F99" s="6">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>181</v>
       </c>
-      <c r="B100">
+      <c r="C100">
         <v>21119</v>
       </c>
-      <c r="D100">
+      <c r="E100">
         <v>3</v>
       </c>
-      <c r="E100" s="6">
-        <v>0</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="F100" s="6">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>178</v>
       </c>
-      <c r="B101">
+      <c r="C101">
         <v>26964</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>3</v>
       </c>
-      <c r="E101" s="6">
-        <v>0</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="F101" s="6">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>178</v>
       </c>
-      <c r="B102">
+      <c r="C102">
         <v>25730</v>
       </c>
-      <c r="D102">
+      <c r="E102">
         <v>3</v>
       </c>
-      <c r="E102" s="6">
-        <v>0</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="F102" s="6">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>177</v>
       </c>
-      <c r="B103">
+      <c r="C103">
         <v>27403</v>
       </c>
-      <c r="D103">
+      <c r="E103">
         <v>2</v>
       </c>
-      <c r="E103" s="6">
-        <v>0</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="F103" s="6">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>177</v>
       </c>
-      <c r="B104">
+      <c r="C104">
         <v>26713</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>3</v>
       </c>
-      <c r="E104" s="6">
-        <v>0</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="F104" s="6">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>177</v>
       </c>
-      <c r="B105">
+      <c r="C105">
         <v>26313</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>2</v>
       </c>
-      <c r="E105" s="6">
-        <v>0</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="F105" s="6">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>177</v>
       </c>
-      <c r="B106">
+      <c r="C106">
         <v>27600</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>2</v>
       </c>
-      <c r="E106" s="6">
-        <v>0</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="F106" s="6">
+        <v>0</v>
+      </c>
+      <c r="G106" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>177</v>
       </c>
-      <c r="B107">
+      <c r="C107">
         <v>27680</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>3</v>
       </c>
-      <c r="E107" s="6">
-        <v>0</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="F107" s="6">
+        <v>0</v>
+      </c>
+      <c r="G107" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>177</v>
       </c>
-      <c r="B108">
+      <c r="C108">
         <v>27891</v>
       </c>
-      <c r="D108">
+      <c r="E108">
         <v>3</v>
       </c>
-      <c r="E108" s="6">
-        <v>0</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="F108" s="6">
+        <v>0</v>
+      </c>
+      <c r="G108" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>177</v>
       </c>
-      <c r="B109">
+      <c r="C109">
         <v>26508</v>
       </c>
-      <c r="D109">
+      <c r="E109">
         <v>2</v>
       </c>
-      <c r="E109" s="6">
-        <v>0</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="F109" s="6">
+        <v>0</v>
+      </c>
+      <c r="G109" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>177</v>
       </c>
-      <c r="B110">
+      <c r="C110">
         <v>27807</v>
       </c>
-      <c r="D110">
+      <c r="E110">
         <v>2</v>
       </c>
-      <c r="E110" s="6">
-        <v>0</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="F110" s="6">
+        <v>0</v>
+      </c>
+      <c r="G110" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>177</v>
       </c>
-      <c r="B111">
+      <c r="C111">
         <v>26510</v>
       </c>
-      <c r="D111">
+      <c r="E111">
         <v>3</v>
       </c>
-      <c r="E111" s="6">
-        <v>0</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="F111" s="6">
+        <v>0</v>
+      </c>
+      <c r="G111" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>177</v>
       </c>
-      <c r="B112">
+      <c r="C112">
         <v>27482</v>
       </c>
-      <c r="D112">
+      <c r="E112">
         <v>3</v>
       </c>
-      <c r="E112" s="6">
-        <v>0</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="F112" s="6">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>177</v>
       </c>
-      <c r="B113">
+      <c r="C113">
         <v>26672</v>
       </c>
-      <c r="D113">
+      <c r="E113">
         <v>2</v>
       </c>
-      <c r="E113" s="6">
-        <v>0</v>
-      </c>
-      <c r="F113" t="s">
+      <c r="F113" s="6">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>176</v>
       </c>
-      <c r="B114">
+      <c r="C114">
         <v>21210</v>
       </c>
-      <c r="D114">
+      <c r="E114">
         <v>2</v>
       </c>
-      <c r="E114" s="6">
-        <v>0</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="F114" s="6">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>176</v>
       </c>
-      <c r="B115">
+      <c r="C115">
         <v>20877</v>
       </c>
-      <c r="D115">
+      <c r="E115">
         <v>2</v>
       </c>
-      <c r="E115" s="6">
-        <v>0</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="F115" s="6">
+        <v>0</v>
+      </c>
+      <c r="G115" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>176</v>
       </c>
-      <c r="B116">
+      <c r="C116">
         <v>20797</v>
       </c>
-      <c r="D116">
+      <c r="E116">
         <v>3</v>
       </c>
-      <c r="E116" s="6">
-        <v>0</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="F116" s="6">
+        <v>0</v>
+      </c>
+      <c r="G116" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>176</v>
       </c>
-      <c r="B117">
+      <c r="C117">
         <v>21567</v>
       </c>
-      <c r="D117">
+      <c r="E117">
         <v>2</v>
       </c>
-      <c r="E117" s="6">
-        <v>0</v>
-      </c>
-      <c r="F117" t="s">
+      <c r="F117" s="6">
+        <v>0</v>
+      </c>
+      <c r="G117" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>176</v>
       </c>
-      <c r="B118">
+      <c r="C118">
         <v>20106</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>3</v>
       </c>
-      <c r="E118" s="6">
-        <v>0</v>
-      </c>
-      <c r="F118" t="s">
+      <c r="F118" s="6">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>176</v>
       </c>
-      <c r="B119">
+      <c r="C119">
         <v>21328</v>
       </c>
-      <c r="D119">
+      <c r="E119">
         <v>2</v>
       </c>
-      <c r="E119" s="6">
-        <v>0</v>
-      </c>
-      <c r="F119" t="s">
+      <c r="F119" s="6">
+        <v>0</v>
+      </c>
+      <c r="G119" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>176</v>
       </c>
-      <c r="B120">
+      <c r="C120">
         <v>20024</v>
       </c>
-      <c r="D120">
+      <c r="E120">
         <v>2</v>
       </c>
-      <c r="E120" s="6">
-        <v>0</v>
-      </c>
-      <c r="F120" t="s">
+      <c r="F120" s="6">
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>182</v>
       </c>
-      <c r="B121">
+      <c r="C121">
         <v>31416</v>
       </c>
-      <c r="D121">
+      <c r="E121">
         <v>3</v>
       </c>
-      <c r="E121" s="6">
-        <v>0</v>
-      </c>
-      <c r="F121" t="s">
+      <c r="F121" s="6">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>182</v>
       </c>
-      <c r="B122">
+      <c r="C122">
         <v>30448</v>
       </c>
-      <c r="D122">
+      <c r="E122">
         <v>3</v>
       </c>
-      <c r="E122" s="6">
-        <v>0</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="F122" s="6">
+        <v>0</v>
+      </c>
+      <c r="G122" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>184</v>
       </c>
-      <c r="B123">
+      <c r="C123">
         <v>23313</v>
       </c>
-      <c r="D123">
+      <c r="E123">
         <v>3</v>
       </c>
-      <c r="E123" s="6">
-        <v>0</v>
-      </c>
-      <c r="F123" t="s">
+      <c r="F123" s="6">
+        <v>0</v>
+      </c>
+      <c r="G123" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>184</v>
       </c>
-      <c r="B124">
+      <c r="C124">
         <v>21665</v>
       </c>
-      <c r="D124">
+      <c r="E124">
         <v>2</v>
       </c>
-      <c r="E124" s="6">
-        <v>0</v>
-      </c>
-      <c r="F124" t="s">
+      <c r="F124" s="6">
+        <v>0</v>
+      </c>
+      <c r="G124" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>184</v>
       </c>
-      <c r="B125">
+      <c r="C125">
         <v>22102</v>
       </c>
-      <c r="D125">
+      <c r="E125">
         <v>3</v>
       </c>
-      <c r="E125" s="6">
-        <v>0</v>
-      </c>
-      <c r="F125" t="s">
+      <c r="F125" s="6">
+        <v>0</v>
+      </c>
+      <c r="G125" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>184</v>
       </c>
-      <c r="B126">
+      <c r="C126">
         <v>22823</v>
       </c>
-      <c r="D126">
+      <c r="E126">
         <v>3</v>
       </c>
-      <c r="E126" s="6">
-        <v>0</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="F126" s="6">
+        <v>0</v>
+      </c>
+      <c r="G126" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>184</v>
       </c>
-      <c r="B127">
+      <c r="C127">
         <v>22337</v>
       </c>
-      <c r="D127">
+      <c r="E127">
         <v>3</v>
       </c>
-      <c r="E127" s="6">
-        <v>0</v>
-      </c>
-      <c r="F127" t="s">
+      <c r="F127" s="6">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>184</v>
       </c>
-      <c r="B128">
+      <c r="C128">
         <v>22618</v>
       </c>
-      <c r="D128">
+      <c r="E128">
         <v>3</v>
       </c>
-      <c r="E128" s="6">
-        <v>0</v>
-      </c>
-      <c r="F128" t="s">
+      <c r="F128" s="6">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>184</v>
       </c>
-      <c r="B129">
+      <c r="C129">
         <v>23109</v>
       </c>
-      <c r="D129">
+      <c r="E129">
         <v>3</v>
       </c>
-      <c r="E129" s="6">
-        <v>0</v>
-      </c>
-      <c r="F129" t="s">
+      <c r="F129" s="6">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
         <v>184</v>
       </c>
-      <c r="B130">
+      <c r="C130">
         <v>21782</v>
       </c>
-      <c r="D130">
+      <c r="E130">
         <v>3</v>
       </c>
-      <c r="E130" s="6">
-        <v>0</v>
-      </c>
-      <c r="F130" t="s">
+      <c r="F130" s="6">
+        <v>0</v>
+      </c>
+      <c r="G130" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>184</v>
       </c>
-      <c r="B131">
+      <c r="C131">
         <v>21580</v>
       </c>
-      <c r="D131">
+      <c r="E131">
         <v>3</v>
       </c>
-      <c r="E131" s="6">
-        <v>0</v>
-      </c>
-      <c r="F131" t="s">
+      <c r="F131" s="6">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>184</v>
       </c>
-      <c r="B132">
+      <c r="C132">
         <v>22802</v>
       </c>
-      <c r="D132">
+      <c r="E132">
         <v>2</v>
       </c>
-      <c r="E132" s="6">
-        <v>0</v>
-      </c>
-      <c r="F132" t="s">
+      <c r="F132" s="6">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>184</v>
       </c>
-      <c r="B133">
+      <c r="C133">
         <v>23024</v>
       </c>
-      <c r="D133">
+      <c r="E133">
         <v>2</v>
       </c>
-      <c r="E133" s="6">
-        <v>0</v>
-      </c>
-      <c r="F133" t="s">
+      <c r="F133" s="6">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>184</v>
       </c>
-      <c r="B134">
+      <c r="C134">
         <v>22149</v>
       </c>
-      <c r="D134">
+      <c r="E134">
         <v>3</v>
       </c>
-      <c r="E134" s="6">
-        <v>0</v>
-      </c>
-      <c r="F134" t="s">
+      <c r="F134" s="6">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>188</v>
       </c>
-      <c r="B135">
+      <c r="C135">
         <v>22307</v>
       </c>
-      <c r="D135">
+      <c r="E135">
         <v>2</v>
       </c>
-      <c r="E135" s="6">
-        <v>0</v>
-      </c>
-      <c r="F135" t="s">
+      <c r="F135" s="6">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>183</v>
       </c>
-      <c r="B136">
+      <c r="C136">
         <v>20858</v>
       </c>
-      <c r="D136">
+      <c r="E136">
         <v>2</v>
       </c>
-      <c r="E136" s="6">
-        <v>0</v>
-      </c>
-      <c r="F136" t="s">
+      <c r="F136" s="6">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>183</v>
       </c>
-      <c r="B137">
+      <c r="C137">
         <v>20645</v>
       </c>
-      <c r="D137">
+      <c r="E137">
         <v>3</v>
       </c>
-      <c r="E137" s="6">
-        <v>0</v>
-      </c>
-      <c r="F137" t="s">
+      <c r="F137" s="6">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
         <v>183</v>
       </c>
-      <c r="B138">
+      <c r="C138">
         <v>21912</v>
       </c>
-      <c r="D138">
+      <c r="E138">
         <v>2</v>
       </c>
-      <c r="E138" s="6">
-        <v>0</v>
-      </c>
-      <c r="F138" t="s">
+      <c r="F138" s="6">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>183</v>
       </c>
-      <c r="B139">
+      <c r="C139">
         <v>20616</v>
       </c>
-      <c r="D139">
+      <c r="E139">
         <v>2</v>
       </c>
-      <c r="E139" s="6">
-        <v>0</v>
-      </c>
-      <c r="F139" t="s">
+      <c r="F139" s="6">
+        <v>0</v>
+      </c>
+      <c r="G139" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
         <v>183</v>
       </c>
-      <c r="B140">
+      <c r="C140">
         <v>21950</v>
       </c>
-      <c r="D140">
+      <c r="E140">
         <v>3</v>
       </c>
-      <c r="E140" s="6">
-        <v>0</v>
-      </c>
-      <c r="F140" t="s">
+      <c r="F140" s="6">
+        <v>0</v>
+      </c>
+      <c r="G140" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>183</v>
       </c>
-      <c r="B141">
+      <c r="C141">
         <v>21079</v>
       </c>
-      <c r="D141">
+      <c r="E141">
         <v>2</v>
       </c>
-      <c r="E141" s="6">
-        <v>0</v>
-      </c>
-      <c r="F141" t="s">
+      <c r="F141" s="6">
+        <v>0</v>
+      </c>
+      <c r="G141" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>183</v>
       </c>
-      <c r="B142">
+      <c r="C142">
         <v>21746</v>
       </c>
-      <c r="D142">
+      <c r="E142">
         <v>3</v>
       </c>
-      <c r="E142" s="6">
-        <v>0</v>
-      </c>
-      <c r="F142" t="s">
+      <c r="F142" s="6">
+        <v>0</v>
+      </c>
+      <c r="G142" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>183</v>
       </c>
-      <c r="B143">
+      <c r="C143">
         <v>22136</v>
       </c>
-      <c r="D143">
+      <c r="E143">
         <v>2</v>
       </c>
-      <c r="E143" s="6">
-        <v>0</v>
-      </c>
-      <c r="F143" t="s">
+      <c r="F143" s="6">
+        <v>0</v>
+      </c>
+      <c r="G143" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>183</v>
       </c>
-      <c r="B144">
+      <c r="C144">
         <v>22422</v>
       </c>
-      <c r="D144">
+      <c r="E144">
         <v>2</v>
       </c>
-      <c r="E144" s="6">
-        <v>0</v>
-      </c>
-      <c r="F144" t="s">
+      <c r="F144" s="6">
+        <v>0</v>
+      </c>
+      <c r="G144" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>183</v>
       </c>
-      <c r="B145">
+      <c r="C145">
         <v>21732</v>
       </c>
-      <c r="D145">
+      <c r="E145">
         <v>2</v>
       </c>
-      <c r="E145" s="6">
-        <v>0</v>
-      </c>
-      <c r="F145" t="s">
+      <c r="F145" s="6">
+        <v>0</v>
+      </c>
+      <c r="G145" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>187</v>
       </c>
-      <c r="B146">
+      <c r="C146">
         <v>22495</v>
       </c>
-      <c r="D146">
+      <c r="E146">
         <v>2</v>
       </c>
-      <c r="E146" s="6">
-        <v>0</v>
-      </c>
-      <c r="F146" t="s">
+      <c r="F146" s="6">
+        <v>0</v>
+      </c>
+      <c r="G146" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>185</v>
       </c>
-      <c r="B147">
+      <c r="C147">
         <v>22576</v>
       </c>
-      <c r="D147">
+      <c r="E147">
         <v>2</v>
       </c>
-      <c r="E147" s="6">
-        <v>0</v>
-      </c>
-      <c r="F147" t="s">
+      <c r="F147" s="6">
+        <v>0</v>
+      </c>
+      <c r="G147" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>185</v>
       </c>
-      <c r="B148">
+      <c r="C148">
         <v>24233</v>
       </c>
-      <c r="D148">
+      <c r="E148">
         <v>2</v>
       </c>
-      <c r="E148" s="6">
-        <v>0</v>
-      </c>
-      <c r="F148" t="s">
+      <c r="F148" s="6">
+        <v>0</v>
+      </c>
+      <c r="G148" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>185</v>
       </c>
-      <c r="B149">
+      <c r="C149">
         <v>24067</v>
       </c>
-      <c r="D149">
+      <c r="E149">
         <v>2</v>
       </c>
-      <c r="E149" s="6">
-        <v>0</v>
-      </c>
-      <c r="F149" t="s">
+      <c r="F149" s="6">
+        <v>0</v>
+      </c>
+      <c r="G149" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>185</v>
       </c>
-      <c r="B150">
+      <c r="C150">
         <v>23233</v>
       </c>
-      <c r="D150">
+      <c r="E150">
         <v>2</v>
       </c>
-      <c r="E150" s="6">
-        <v>0</v>
-      </c>
-      <c r="F150" t="s">
+      <c r="F150" s="6">
+        <v>0</v>
+      </c>
+      <c r="G150" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>185</v>
       </c>
-      <c r="B151">
+      <c r="C151">
         <v>24437</v>
       </c>
-      <c r="D151">
+      <c r="E151">
         <v>2</v>
       </c>
-      <c r="E151" s="6">
-        <v>0</v>
-      </c>
-      <c r="F151" t="s">
+      <c r="F151" s="6">
+        <v>0</v>
+      </c>
+      <c r="G151" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>185</v>
       </c>
-      <c r="B152">
+      <c r="C152">
         <v>22575</v>
       </c>
-      <c r="D152">
+      <c r="E152">
         <v>3</v>
       </c>
-      <c r="E152" s="6">
-        <v>0</v>
-      </c>
-      <c r="F152" t="s">
+      <c r="F152" s="6">
+        <v>0</v>
+      </c>
+      <c r="G152" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>185</v>
       </c>
-      <c r="B153">
+      <c r="C153">
         <v>22379</v>
       </c>
-      <c r="D153">
+      <c r="E153">
         <v>3</v>
       </c>
-      <c r="E153" s="6">
-        <v>0</v>
-      </c>
-      <c r="F153" t="s">
+      <c r="F153" s="6">
+        <v>0</v>
+      </c>
+      <c r="G153" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>185</v>
       </c>
-      <c r="B154">
+      <c r="C154">
         <v>23987</v>
       </c>
-      <c r="D154">
+      <c r="E154">
         <v>3</v>
       </c>
-      <c r="E154" s="6">
-        <v>0</v>
-      </c>
-      <c r="F154" t="s">
+      <c r="F154" s="6">
+        <v>0</v>
+      </c>
+      <c r="G154" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
         <v>185</v>
       </c>
-      <c r="B155">
+      <c r="C155">
         <v>23433</v>
       </c>
-      <c r="D155">
+      <c r="E155">
         <v>3</v>
       </c>
-      <c r="E155" s="6">
-        <v>0</v>
-      </c>
-      <c r="F155" t="s">
+      <c r="F155" s="6">
+        <v>0</v>
+      </c>
+      <c r="G155" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>185</v>
       </c>
-      <c r="B156">
+      <c r="C156">
         <v>22822</v>
       </c>
-      <c r="D156">
+      <c r="E156">
         <v>3</v>
       </c>
-      <c r="E156" s="6">
-        <v>0</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="F156" s="6">
+        <v>0</v>
+      </c>
+      <c r="G156" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>185</v>
       </c>
-      <c r="B157">
+      <c r="C157">
         <v>23106</v>
       </c>
-      <c r="D157">
+      <c r="E157">
         <v>3</v>
       </c>
-      <c r="E157" s="6">
-        <v>0</v>
-      </c>
-      <c r="F157" t="s">
+      <c r="F157" s="6">
+        <v>0</v>
+      </c>
+      <c r="G157" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>185</v>
       </c>
-      <c r="B158">
+      <c r="C158">
         <v>24847</v>
       </c>
-      <c r="D158">
+      <c r="E158">
         <v>3</v>
       </c>
-      <c r="E158" s="6">
-        <v>0</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="F158" s="6">
+        <v>0</v>
+      </c>
+      <c r="G158" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>185</v>
       </c>
-      <c r="B159">
+      <c r="C159">
         <v>23680</v>
       </c>
-      <c r="D159">
+      <c r="E159">
         <v>2</v>
       </c>
-      <c r="E159" s="6">
-        <v>0</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="F159" s="6">
+        <v>0</v>
+      </c>
+      <c r="G159" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>185</v>
       </c>
-      <c r="B160">
+      <c r="C160">
         <v>22783</v>
       </c>
-      <c r="D160">
+      <c r="E160">
         <v>2</v>
       </c>
-      <c r="E160" s="6">
-        <v>0</v>
-      </c>
-      <c r="F160" t="s">
+      <c r="F160" s="6">
+        <v>0</v>
+      </c>
+      <c r="G160" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>185</v>
       </c>
-      <c r="B161">
+      <c r="C161">
         <v>23870</v>
       </c>
-      <c r="D161">
+      <c r="E161">
         <v>2</v>
       </c>
-      <c r="E161" s="6">
-        <v>0</v>
-      </c>
-      <c r="F161" t="s">
+      <c r="F161" s="6">
+        <v>0</v>
+      </c>
+      <c r="G161" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:7">
       <c r="A162" t="s">
         <v>185</v>
       </c>
-      <c r="B162">
+      <c r="C162">
         <v>22397</v>
       </c>
-      <c r="D162">
+      <c r="E162">
         <v>2</v>
       </c>
-      <c r="E162" s="6">
-        <v>0</v>
-      </c>
-      <c r="F162" t="s">
+      <c r="F162" s="6">
+        <v>0</v>
+      </c>
+      <c r="G162" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:7">
       <c r="A163" t="s">
         <v>185</v>
       </c>
-      <c r="B163">
+      <c r="C163">
         <v>22983</v>
       </c>
-      <c r="D163">
+      <c r="E163">
         <v>2</v>
       </c>
-      <c r="E163" s="6">
-        <v>0</v>
-      </c>
-      <c r="F163" t="s">
+      <c r="F163" s="6">
+        <v>0</v>
+      </c>
+      <c r="G163" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:7">
       <c r="A164" t="s">
         <v>185</v>
       </c>
-      <c r="B164">
+      <c r="C164">
         <v>23825</v>
       </c>
-      <c r="D164">
+      <c r="E164">
         <v>3</v>
       </c>
-      <c r="E164" s="6">
-        <v>0</v>
-      </c>
-      <c r="F164" t="s">
+      <c r="F164" s="6">
+        <v>0</v>
+      </c>
+      <c r="G164" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:7">
       <c r="A165" t="s">
         <v>185</v>
       </c>
-      <c r="B165">
+      <c r="C165">
         <v>23454</v>
       </c>
-      <c r="D165">
+      <c r="E165">
         <v>2</v>
       </c>
-      <c r="E165" s="6">
-        <v>0</v>
-      </c>
-      <c r="F165" t="s">
+      <c r="F165" s="6">
+        <v>0</v>
+      </c>
+      <c r="G165" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>185</v>
       </c>
-      <c r="B166">
+      <c r="C166">
         <v>23701</v>
       </c>
-      <c r="D166">
+      <c r="E166">
         <v>3</v>
       </c>
-      <c r="E166" s="6">
-        <v>0</v>
-      </c>
-      <c r="F166" t="s">
+      <c r="F166" s="6">
+        <v>0</v>
+      </c>
+      <c r="G166" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>186</v>
       </c>
-      <c r="B167">
+      <c r="C167">
         <v>23063</v>
       </c>
-      <c r="D167">
+      <c r="E167">
         <v>2</v>
       </c>
-      <c r="E167" s="6">
-        <v>0</v>
-      </c>
-      <c r="F167" t="s">
+      <c r="F167" s="6">
+        <v>0</v>
+      </c>
+      <c r="G167" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
         <v>186</v>
       </c>
-      <c r="B168">
+      <c r="C168">
         <v>22824</v>
       </c>
-      <c r="D168">
+      <c r="E168">
         <v>2</v>
       </c>
-      <c r="E168" s="6">
-        <v>0</v>
-      </c>
-      <c r="F168" t="s">
+      <c r="F168" s="6">
+        <v>0</v>
+      </c>
+      <c r="G168" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
         <v>186</v>
       </c>
-      <c r="B169">
+      <c r="C169">
         <v>24475</v>
       </c>
-      <c r="D169">
+      <c r="E169">
         <v>3</v>
       </c>
-      <c r="E169" s="6">
-        <v>0</v>
-      </c>
-      <c r="F169" t="s">
+      <c r="F169" s="6">
+        <v>0</v>
+      </c>
+      <c r="G169" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>161</v>
       </c>
-      <c r="B170">
+      <c r="C170">
         <v>12012</v>
       </c>
-      <c r="D170">
+      <c r="E170">
         <v>2</v>
       </c>
-      <c r="E170" s="6">
-        <v>0</v>
-      </c>
-      <c r="F170" t="s">
+      <c r="F170" s="6">
+        <v>0</v>
+      </c>
+      <c r="G170" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>161</v>
       </c>
-      <c r="B171">
+      <c r="C171">
         <v>14168</v>
       </c>
-      <c r="D171">
+      <c r="E171">
         <v>2</v>
       </c>
-      <c r="E171" s="6">
-        <v>0</v>
-      </c>
-      <c r="F171" t="s">
+      <c r="F171" s="6">
+        <v>0</v>
+      </c>
+      <c r="G171" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>161</v>
       </c>
-      <c r="B172">
+      <c r="C172">
         <v>12180</v>
       </c>
-      <c r="D172">
+      <c r="E172">
         <v>2</v>
       </c>
-      <c r="E172" s="6">
-        <v>0</v>
-      </c>
-      <c r="F172" t="s">
+      <c r="F172" s="6">
+        <v>0</v>
+      </c>
+      <c r="G172" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>161</v>
       </c>
-      <c r="B173">
+      <c r="C173">
         <v>12333</v>
       </c>
-      <c r="D173">
+      <c r="E173">
         <v>2</v>
       </c>
-      <c r="E173" s="6">
-        <v>0</v>
-      </c>
-      <c r="F173" t="s">
+      <c r="F173" s="6">
+        <v>0</v>
+      </c>
+      <c r="G173" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>161</v>
       </c>
-      <c r="B174">
+      <c r="C174">
         <v>14318</v>
       </c>
-      <c r="D174">
+      <c r="E174">
         <v>2</v>
       </c>
-      <c r="E174" s="6">
-        <v>0</v>
-      </c>
-      <c r="F174" t="s">
+      <c r="F174" s="6">
+        <v>0</v>
+      </c>
+      <c r="G174" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>161</v>
       </c>
-      <c r="B175">
+      <c r="C175">
         <v>10595</v>
       </c>
-      <c r="D175">
+      <c r="E175">
         <v>2</v>
       </c>
-      <c r="E175" s="6">
-        <v>0</v>
-      </c>
-      <c r="F175" t="s">
+      <c r="F175" s="6">
+        <v>0</v>
+      </c>
+      <c r="G175" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>161</v>
       </c>
-      <c r="B176">
+      <c r="C176">
         <v>16688</v>
       </c>
-      <c r="D176">
+      <c r="E176">
         <v>2</v>
       </c>
-      <c r="E176" s="6">
-        <v>0</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="F176" s="6">
+        <v>0</v>
+      </c>
+      <c r="G176" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>161</v>
       </c>
-      <c r="B177">
+      <c r="C177">
         <v>10914</v>
       </c>
-      <c r="D177">
+      <c r="E177">
         <v>2</v>
       </c>
-      <c r="E177" s="6">
-        <v>0</v>
-      </c>
-      <c r="F177" t="s">
+      <c r="F177" s="6">
+        <v>0</v>
+      </c>
+      <c r="G177" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>161</v>
       </c>
-      <c r="B178">
+      <c r="C178">
         <v>10753</v>
       </c>
-      <c r="D178">
+      <c r="E178">
         <v>2</v>
       </c>
-      <c r="E178" s="6">
-        <v>0</v>
-      </c>
-      <c r="F178" t="s">
+      <c r="F178" s="6">
+        <v>0</v>
+      </c>
+      <c r="G178" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:7">
       <c r="A179" t="s">
         <v>164</v>
       </c>
-      <c r="B179">
+      <c r="C179">
         <v>13537</v>
       </c>
-      <c r="D179">
+      <c r="E179">
         <v>2</v>
       </c>
-      <c r="E179" s="6">
-        <v>0</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="F179" s="6">
+        <v>0</v>
+      </c>
+      <c r="G179" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:7">
       <c r="A180" t="s">
         <v>164</v>
       </c>
-      <c r="B180">
+      <c r="C180">
         <v>14260</v>
       </c>
-      <c r="D180">
+      <c r="E180">
         <v>2</v>
       </c>
-      <c r="E180" s="6">
-        <v>0</v>
-      </c>
-      <c r="F180" t="s">
+      <c r="F180" s="6">
+        <v>0</v>
+      </c>
+      <c r="G180" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:7">
       <c r="A181" t="s">
         <v>164</v>
       </c>
-      <c r="B181">
+      <c r="C181">
         <v>12181</v>
       </c>
-      <c r="D181">
+      <c r="E181">
         <v>2</v>
       </c>
-      <c r="E181" s="6">
-        <v>0</v>
-      </c>
-      <c r="F181" t="s">
+      <c r="F181" s="6">
+        <v>0</v>
+      </c>
+      <c r="G181" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:7">
       <c r="A182" t="s">
         <v>164</v>
       </c>
-      <c r="B182">
+      <c r="C182">
         <v>12332</v>
       </c>
-      <c r="D182">
+      <c r="E182">
         <v>2</v>
       </c>
-      <c r="E182" s="6">
-        <v>0</v>
-      </c>
-      <c r="F182" t="s">
+      <c r="F182" s="6">
+        <v>0</v>
+      </c>
+      <c r="G182" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:7">
       <c r="A183" t="s">
         <v>164</v>
       </c>
-      <c r="B183">
+      <c r="C183">
         <v>14419</v>
       </c>
-      <c r="D183">
+      <c r="E183">
         <v>2</v>
       </c>
-      <c r="E183" s="6">
-        <v>0</v>
-      </c>
-      <c r="F183" t="s">
+      <c r="F183" s="6">
+        <v>0</v>
+      </c>
+      <c r="G183" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:7">
       <c r="A184" t="s">
         <v>164</v>
       </c>
-      <c r="B184">
+      <c r="C184">
         <v>14577</v>
       </c>
-      <c r="D184">
+      <c r="E184">
         <v>2</v>
       </c>
-      <c r="E184" s="6">
-        <v>0</v>
-      </c>
-      <c r="F184" t="s">
+      <c r="F184" s="6">
+        <v>0</v>
+      </c>
+      <c r="G184" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:7">
       <c r="A185" t="s">
         <v>164</v>
       </c>
-      <c r="B185">
+      <c r="C185">
         <v>15628</v>
       </c>
-      <c r="D185">
+      <c r="E185">
         <v>2</v>
       </c>
-      <c r="E185" s="6">
-        <v>0</v>
-      </c>
-      <c r="F185" t="s">
+      <c r="F185" s="6">
+        <v>0</v>
+      </c>
+      <c r="G185" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:7">
       <c r="A186" t="s">
         <v>164</v>
       </c>
-      <c r="B186">
+      <c r="C186">
         <v>15447</v>
       </c>
-      <c r="D186">
+      <c r="E186">
         <v>2</v>
       </c>
-      <c r="E186" s="6">
-        <v>0</v>
-      </c>
-      <c r="F186" t="s">
+      <c r="F186" s="6">
+        <v>0</v>
+      </c>
+      <c r="G186" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:7">
       <c r="A187" t="s">
         <v>163</v>
       </c>
-      <c r="B187">
+      <c r="C187">
         <v>12367</v>
       </c>
-      <c r="D187">
+      <c r="E187">
         <v>2</v>
       </c>
-      <c r="E187" s="6">
-        <v>0</v>
-      </c>
-      <c r="F187" t="s">
+      <c r="F187" s="6">
+        <v>0</v>
+      </c>
+      <c r="G187" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:7">
       <c r="A188" t="s">
         <v>166</v>
       </c>
-      <c r="B188">
+      <c r="C188">
         <v>18895</v>
       </c>
-      <c r="D188">
+      <c r="E188">
         <v>2</v>
       </c>
-      <c r="E188" s="6">
-        <v>0</v>
-      </c>
-      <c r="F188" t="s">
+      <c r="F188" s="6">
+        <v>0</v>
+      </c>
+      <c r="G188" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:7">
       <c r="A189" t="s">
         <v>166</v>
       </c>
-      <c r="B189">
+      <c r="C189">
         <v>17499</v>
       </c>
-      <c r="D189">
+      <c r="E189">
         <v>2</v>
       </c>
-      <c r="E189" s="6">
-        <v>0</v>
-      </c>
-      <c r="F189" t="s">
+      <c r="F189" s="6">
+        <v>0</v>
+      </c>
+      <c r="G189" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:7">
       <c r="A190" t="s">
         <v>166</v>
       </c>
-      <c r="B190">
+      <c r="C190">
         <v>17649</v>
       </c>
-      <c r="D190">
+      <c r="E190">
         <v>2</v>
       </c>
-      <c r="E190" s="6">
-        <v>0</v>
-      </c>
-      <c r="F190" t="s">
+      <c r="F190" s="6">
+        <v>0</v>
+      </c>
+      <c r="G190" t="s">
         <v>191</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{6820557B-6CE2-4FD8-86A4-E2CD52A6D2FD}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J190">
+  <autoFilter ref="A1:K1" xr:uid="{6820557B-6CE2-4FD8-86A4-E2CD52A6D2FD}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K190">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
@@ -8166,1467 +8269,124 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D125B437-E159-4E97-8559-08AC52B2F723}">
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="3" max="3" width="23.125" customWidth="1"/>
     <col min="4" max="4" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>314</v>
       </c>
       <c r="B1" t="s">
         <v>155</v>
       </c>
       <c r="C1" t="s">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="D1" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="E1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="C2">
-        <v>189.1121</v>
+      <c r="A2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="C3">
-        <v>205.1071</v>
+      <c r="A3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" t="s">
+        <v>247</v>
+      </c>
       <c r="C4">
-        <v>219.12270000000001</v>
+        <v>260.14920000000001</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="C5">
-        <v>246.1336</v>
+        <v>344.17039999999997</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>374.18099999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B7" t="s">
         <v>247</v>
       </c>
-      <c r="C6">
-        <v>260.14920000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
       <c r="C7">
-        <v>264.14420000000001</v>
+        <v>376.19659999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" t="s">
+        <v>247</v>
+      </c>
       <c r="C8">
-        <v>278.15980000000002</v>
+        <v>406.2072</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="C9">
-        <v>303.1438</v>
+        <v>566.28070000000002</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>249</v>
-      </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
       <c r="C10">
-        <v>335.17</v>
+        <v>580.29639999999995</v>
+      </c>
+      <c r="D10" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>319</v>
+      </c>
+      <c r="B11" t="s">
+        <v>316</v>
+      </c>
       <c r="C11">
-        <v>344.17039999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="C12">
-        <v>374.18099999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C13">
-        <v>376.19659999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>251</v>
-      </c>
-      <c r="B14" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14">
-        <v>406.2072</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="C15">
-        <v>409.20679999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="C16">
-        <v>420.22280000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17">
-        <v>423.22250000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18">
-        <v>450.23340000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19">
-        <v>452.24900000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20">
-        <v>464.24900000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21">
-        <v>509.27050000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22">
-        <v>523.28610000000003</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23">
-        <v>566.28070000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24">
-        <v>580.29639999999995</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25">
-        <v>596.29129999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26">
-        <v>624.32259999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27">
-        <v>638.33820000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="3:3">
-      <c r="C28">
-        <v>654.33309999999994</v>
-      </c>
-    </row>
-    <row r="29" spans="3:3">
-      <c r="C29">
-        <v>668.34879999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="3:3">
-      <c r="C30">
-        <v>697.37530000000004</v>
-      </c>
-    </row>
-    <row r="31" spans="3:3">
-      <c r="C31">
-        <v>713.37030000000004</v>
-      </c>
-    </row>
-    <row r="32" spans="3:3">
-      <c r="C32">
-        <v>755.89099999999996</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4">
-      <c r="C33">
-        <v>756.38300000000004</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4">
-      <c r="C34">
-        <v>770.8963</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4">
-      <c r="C35">
-        <v>776.8963</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4">
-      <c r="C36">
-        <v>777.90409999999997</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4">
-      <c r="C37">
-        <v>784.39670000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4">
-      <c r="C38">
-        <v>785.90160000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4">
-      <c r="C39">
-        <v>793.39660000000003</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4">
-      <c r="C40">
-        <v>798.41740000000004</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4">
-      <c r="C41">
-        <v>799.40139999999997</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4">
-      <c r="C42">
-        <v>804.41740000000004</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4">
-      <c r="C43">
-        <v>806.41489999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4">
-      <c r="C44">
-        <v>811.40700000000004</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4">
-      <c r="C45" s="6">
-        <v>814.4067</v>
-      </c>
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" spans="3:4">
-      <c r="C46">
         <v>825.42269999999996</v>
       </c>
-    </row>
-    <row r="47" spans="3:4">
-      <c r="C47">
-        <v>828.42240000000004</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4">
-      <c r="C48">
-        <v>834.92</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4">
-      <c r="C49">
-        <v>842.43799999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4">
-      <c r="C50">
-        <v>843.42759999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4">
-      <c r="C51">
-        <v>850.43550000000005</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4">
-      <c r="C52">
-        <v>857.94090000000006</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4">
-      <c r="C53" s="6">
-        <v>858.43290000000002</v>
-      </c>
-      <c r="D53" s="6"/>
-    </row>
-    <row r="54" spans="3:4">
-      <c r="C54">
-        <v>863.94090000000006</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4">
-      <c r="C55">
-        <v>864.43849999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4">
-      <c r="C56">
-        <v>864.94870000000003</v>
-      </c>
-    </row>
-    <row r="57" spans="3:4">
-      <c r="C57">
-        <v>871.44640000000004</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4">
-      <c r="C58">
-        <v>872.44860000000006</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4">
-      <c r="C59">
-        <v>872.94619999999998</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4">
-      <c r="C60">
-        <v>878.94619999999998</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4">
-      <c r="C61">
-        <v>879.95399999999995</v>
-      </c>
-    </row>
-    <row r="62" spans="3:4">
-      <c r="C62">
-        <v>887.45950000000005</v>
-      </c>
-    </row>
-    <row r="63" spans="3:4">
-      <c r="C63">
-        <v>887.95150000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="3:4">
-      <c r="C64">
-        <v>893.45950000000005</v>
-      </c>
-    </row>
-    <row r="65" spans="3:3">
-      <c r="C65">
-        <v>899.45950000000005</v>
-      </c>
-    </row>
-    <row r="66" spans="3:3">
-      <c r="C66">
-        <v>900.46730000000002</v>
-      </c>
-    </row>
-    <row r="67" spans="3:3">
-      <c r="C67">
-        <v>901.45129999999995</v>
-      </c>
-    </row>
-    <row r="68" spans="3:3">
-      <c r="C68">
-        <v>908.46479999999997</v>
-      </c>
-    </row>
-    <row r="69" spans="3:3">
-      <c r="C69">
-        <v>916.45659999999998</v>
-      </c>
-    </row>
-    <row r="70" spans="3:3">
-      <c r="C70">
-        <v>917.47</v>
-      </c>
-    </row>
-    <row r="71" spans="3:3">
-      <c r="C71">
-        <v>921.96460000000002</v>
-      </c>
-    </row>
-    <row r="72" spans="3:3">
-      <c r="C72">
-        <v>935.98590000000002</v>
-      </c>
-    </row>
-    <row r="73" spans="3:3">
-      <c r="C73">
-        <v>936.96990000000005</v>
-      </c>
-    </row>
-    <row r="74" spans="3:3">
-      <c r="C74">
-        <v>943.97770000000003</v>
-      </c>
-    </row>
-    <row r="75" spans="3:3">
-      <c r="C75">
-        <v>945.47749999999996</v>
-      </c>
-    </row>
-    <row r="76" spans="3:3">
-      <c r="C76">
-        <v>951.48310000000004</v>
-      </c>
-    </row>
-    <row r="77" spans="3:3">
-      <c r="C77">
-        <v>957.48310000000004</v>
-      </c>
-    </row>
-    <row r="78" spans="3:3">
-      <c r="C78">
-        <v>958.49099999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="3:3">
-      <c r="C79">
-        <v>959.99080000000004</v>
-      </c>
-    </row>
-    <row r="80" spans="3:3">
-      <c r="C80">
-        <v>965.99080000000004</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3">
-      <c r="C81">
-        <v>966.48839999999996</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3">
-      <c r="C82">
-        <v>966.99860000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="3:3">
-      <c r="C83">
-        <v>972.99860000000001</v>
-      </c>
-    </row>
-    <row r="84" spans="3:3">
-      <c r="C84">
-        <v>973.49620000000004</v>
-      </c>
-    </row>
-    <row r="85" spans="3:3">
-      <c r="C85">
-        <v>974.99609999999996</v>
-      </c>
-    </row>
-    <row r="86" spans="3:3">
-      <c r="C86">
-        <v>980.50409999999999</v>
-      </c>
-    </row>
-    <row r="87" spans="3:3">
-      <c r="C87">
-        <v>980.99609999999996</v>
-      </c>
-    </row>
-    <row r="88" spans="3:3">
-      <c r="C88">
-        <v>981.49369999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="3:3">
-      <c r="C89">
-        <v>982.00390000000004</v>
-      </c>
-    </row>
-    <row r="90" spans="3:3">
-      <c r="C90">
-        <v>985.49620000000004</v>
-      </c>
-    </row>
-    <row r="91" spans="3:3">
-      <c r="C91">
-        <v>995.50940000000003</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3">
-      <c r="C92">
-        <v>1002.5172</v>
-      </c>
-    </row>
-    <row r="93" spans="3:3">
-      <c r="C93">
-        <v>1010.5146</v>
-      </c>
-    </row>
-    <row r="94" spans="3:3">
-      <c r="C94">
-        <v>1015.5068</v>
-      </c>
-    </row>
-    <row r="95" spans="3:3">
-      <c r="C95">
-        <v>1024.0145</v>
-      </c>
-    </row>
-    <row r="96" spans="3:3">
-      <c r="C96">
-        <v>1029.5225</v>
-      </c>
-    </row>
-    <row r="97" spans="3:3">
-      <c r="C97">
-        <v>1030.0382999999999</v>
-      </c>
-    </row>
-    <row r="98" spans="3:3">
-      <c r="C98">
-        <v>1032.5220999999999</v>
-      </c>
-    </row>
-    <row r="99" spans="3:3">
-      <c r="C99">
-        <v>1039.0198</v>
-      </c>
-    </row>
-    <row r="100" spans="3:3">
-      <c r="C100">
-        <v>1044.5277000000001</v>
-      </c>
-    </row>
-    <row r="101" spans="3:3">
-      <c r="C101">
-        <v>1045.5174</v>
-      </c>
-    </row>
-    <row r="102" spans="3:3">
-      <c r="C102">
-        <v>1046.0275999999999</v>
-      </c>
-    </row>
-    <row r="103" spans="3:3">
-      <c r="C103">
-        <v>1053.5329999999999</v>
-      </c>
-    </row>
-    <row r="104" spans="3:3">
-      <c r="C104">
-        <v>1059.5329999999999</v>
-      </c>
-    </row>
-    <row r="105" spans="3:3">
-      <c r="C105">
-        <v>1060.5409</v>
-      </c>
-    </row>
-    <row r="106" spans="3:3">
-      <c r="C106">
-        <v>1062.5327</v>
-      </c>
-    </row>
-    <row r="107" spans="3:3">
-      <c r="C107">
-        <v>1066.5409</v>
-      </c>
-    </row>
-    <row r="108" spans="3:3">
-      <c r="C108">
-        <v>1068.0407</v>
-      </c>
-    </row>
-    <row r="109" spans="3:3">
-      <c r="C109">
-        <v>1068.5382999999999</v>
-      </c>
-    </row>
-    <row r="110" spans="3:3">
-      <c r="C110">
-        <v>1069.0485000000001</v>
-      </c>
-    </row>
-    <row r="111" spans="3:3">
-      <c r="C111">
-        <v>1075.5461</v>
-      </c>
-    </row>
-    <row r="112" spans="3:3">
-      <c r="C112">
-        <v>1082.5540000000001</v>
-      </c>
-    </row>
-    <row r="113" spans="3:3">
-      <c r="C113">
-        <v>1083.5436</v>
-      </c>
-    </row>
-    <row r="114" spans="3:3">
-      <c r="C114">
-        <v>1089.0516</v>
-      </c>
-    </row>
-    <row r="115" spans="3:3">
-      <c r="C115">
-        <v>1091.5591999999999</v>
-      </c>
-    </row>
-    <row r="116" spans="3:3">
-      <c r="C116">
-        <v>1097.5591999999999</v>
-      </c>
-    </row>
-    <row r="117" spans="3:3">
-      <c r="C117">
-        <v>1103.5591999999999</v>
-      </c>
-    </row>
-    <row r="118" spans="3:3">
-      <c r="C118">
-        <v>1104.5671</v>
-      </c>
-    </row>
-    <row r="119" spans="3:3">
-      <c r="C119">
-        <v>1111.0590999999999</v>
-      </c>
-    </row>
-    <row r="120" spans="3:3">
-      <c r="C120">
-        <v>1112.5645</v>
-      </c>
-    </row>
-    <row r="121" spans="3:3">
-      <c r="C121">
-        <v>1117.5567000000001</v>
-      </c>
-    </row>
-    <row r="122" spans="3:3">
-      <c r="C122">
-        <v>1121.5698</v>
-      </c>
-    </row>
-    <row r="123" spans="3:3">
-      <c r="C123">
-        <v>1124.5645</v>
-      </c>
-    </row>
-    <row r="124" spans="3:3">
-      <c r="C124">
-        <v>1126.5907</v>
-      </c>
-    </row>
-    <row r="125" spans="3:3">
-      <c r="C125">
-        <v>1132.5858000000001</v>
-      </c>
-    </row>
-    <row r="126" spans="3:3">
-      <c r="C126">
-        <v>1133.0722000000001</v>
-      </c>
-    </row>
-    <row r="127" spans="3:3">
-      <c r="C127">
-        <v>1141.0696</v>
-      </c>
-    </row>
-    <row r="128" spans="3:3">
-      <c r="C128">
-        <v>1144.5858000000001</v>
-      </c>
-    </row>
-    <row r="129" spans="3:3">
-      <c r="C129">
-        <v>1146.5776000000001</v>
-      </c>
-    </row>
-    <row r="130" spans="3:3">
-      <c r="C130">
-        <v>1161.5829000000001</v>
-      </c>
-    </row>
-    <row r="131" spans="3:3">
-      <c r="C131">
-        <v>1162.5907</v>
-      </c>
-    </row>
-    <row r="132" spans="3:3">
-      <c r="C132">
-        <v>1162.5963999999999</v>
-      </c>
-    </row>
-    <row r="133" spans="3:3">
-      <c r="C133">
-        <v>1168.5907</v>
-      </c>
-    </row>
-    <row r="134" spans="3:3">
-      <c r="C134">
-        <v>1176.0962</v>
-      </c>
-    </row>
-    <row r="135" spans="3:3">
-      <c r="C135">
-        <v>1177.596</v>
-      </c>
-    </row>
-    <row r="136" spans="3:3">
-      <c r="C136">
-        <v>1183.104</v>
-      </c>
-    </row>
-    <row r="137" spans="3:3">
-      <c r="C137">
-        <v>1184.6038000000001</v>
-      </c>
-    </row>
-    <row r="138" spans="3:3">
-      <c r="C138">
-        <v>1189.596</v>
-      </c>
-    </row>
-    <row r="139" spans="3:3">
-      <c r="C139">
-        <v>1191.1015</v>
-      </c>
-    </row>
-    <row r="140" spans="3:3">
-      <c r="C140">
-        <v>1191.6116999999999</v>
-      </c>
-    </row>
-    <row r="141" spans="3:3">
-      <c r="C141">
-        <v>1198.1093000000001</v>
-      </c>
-    </row>
-    <row r="142" spans="3:3">
-      <c r="C142">
-        <v>1198.6195</v>
-      </c>
-    </row>
-    <row r="143" spans="3:3">
-      <c r="C143">
-        <v>1199.6090999999999</v>
-      </c>
-    </row>
-    <row r="144" spans="3:3">
-      <c r="C144">
-        <v>1203.6116999999999</v>
-      </c>
-    </row>
-    <row r="145" spans="3:4">
-      <c r="C145">
-        <v>1206.617</v>
-      </c>
-    </row>
-    <row r="146" spans="3:4">
-      <c r="C146" s="6">
-        <v>1219.6066000000001</v>
-      </c>
-      <c r="D146" s="6"/>
-    </row>
-    <row r="147" spans="3:4">
-      <c r="C147">
-        <v>1226.6143999999999</v>
-      </c>
-    </row>
-    <row r="148" spans="3:4">
-      <c r="C148" s="6">
-        <v>1233.6222</v>
-      </c>
-      <c r="D148" s="6"/>
-    </row>
-    <row r="149" spans="3:4">
-      <c r="C149">
-        <v>1236.6219000000001</v>
-      </c>
-    </row>
-    <row r="150" spans="3:4">
-      <c r="C150">
-        <v>1240.1198999999999</v>
-      </c>
-    </row>
-    <row r="151" spans="3:4">
-      <c r="C151">
-        <v>1247.1277</v>
-      </c>
-    </row>
-    <row r="152" spans="3:4">
-      <c r="C152">
-        <v>1248.6275000000001</v>
-      </c>
-    </row>
-    <row r="153" spans="3:4">
-      <c r="C153">
-        <v>1249.6171999999999</v>
-      </c>
-    </row>
-    <row r="154" spans="3:4">
-      <c r="C154">
-        <v>1255.6352999999999</v>
-      </c>
-    </row>
-    <row r="155" spans="3:4">
-      <c r="C155">
-        <v>1263.1407999999999</v>
-      </c>
-    </row>
-    <row r="156" spans="3:4">
-      <c r="C156">
-        <v>1263.6328000000001</v>
-      </c>
-    </row>
-    <row r="157" spans="3:4">
-      <c r="C157">
-        <v>1266.6324999999999</v>
-      </c>
-    </row>
-    <row r="158" spans="3:4">
-      <c r="C158">
-        <v>1270.1486</v>
-      </c>
-    </row>
-    <row r="159" spans="3:4">
-      <c r="C159">
-        <v>1277.6485</v>
-      </c>
-    </row>
-    <row r="160" spans="3:4">
-      <c r="C160">
-        <v>1278.1460999999999</v>
-      </c>
-    </row>
-    <row r="161" spans="3:3">
-      <c r="C161">
-        <v>1285.1539</v>
-      </c>
-    </row>
-    <row r="162" spans="3:3">
-      <c r="C162">
-        <v>1292.1617000000001</v>
-      </c>
-    </row>
-    <row r="163" spans="3:3">
-      <c r="C163">
-        <v>1293.1514</v>
-      </c>
-    </row>
-    <row r="164" spans="3:3">
-      <c r="C164">
-        <v>1293.6615999999999</v>
-      </c>
-    </row>
-    <row r="165" spans="3:3">
-      <c r="C165">
-        <v>1295.6590000000001</v>
-      </c>
-    </row>
-    <row r="166" spans="3:3">
-      <c r="C166">
-        <v>1300.1592000000001</v>
-      </c>
-    </row>
-    <row r="167" spans="3:3">
-      <c r="C167">
-        <v>1301.6590000000001</v>
-      </c>
-    </row>
-    <row r="168" spans="3:3">
-      <c r="C168">
-        <v>1307.6590000000001</v>
-      </c>
-    </row>
-    <row r="169" spans="3:3">
-      <c r="C169">
-        <v>1315.1587999999999</v>
-      </c>
-    </row>
-    <row r="170" spans="3:3">
-      <c r="C170">
-        <v>1328.6642999999999</v>
-      </c>
-    </row>
-    <row r="171" spans="3:3">
-      <c r="C171">
-        <v>1330.1641</v>
-      </c>
-    </row>
-    <row r="172" spans="3:3">
-      <c r="C172">
-        <v>1336.6856</v>
-      </c>
-    </row>
-    <row r="173" spans="3:3">
-      <c r="C173">
-        <v>1342.1696999999999</v>
-      </c>
-    </row>
-    <row r="174" spans="3:3">
-      <c r="C174">
-        <v>1348.6856</v>
-      </c>
-    </row>
-    <row r="175" spans="3:3">
-      <c r="C175">
-        <v>1349.1776</v>
-      </c>
-    </row>
-    <row r="176" spans="3:3">
-      <c r="C176">
-        <v>1362.7012</v>
-      </c>
-    </row>
-    <row r="177" spans="3:4">
-      <c r="C177">
-        <v>1366.6960999999999</v>
-      </c>
-    </row>
-    <row r="178" spans="3:4">
-      <c r="C178">
-        <v>1371.6883</v>
-      </c>
-    </row>
-    <row r="179" spans="3:4">
-      <c r="C179">
-        <v>1372.1985</v>
-      </c>
-    </row>
-    <row r="180" spans="3:4">
-      <c r="C180">
-        <v>1378.6960999999999</v>
-      </c>
-    </row>
-    <row r="181" spans="3:4">
-      <c r="C181">
-        <v>1380.1959999999999</v>
-      </c>
-    </row>
-    <row r="182" spans="3:4">
-      <c r="C182">
-        <v>1387.2038</v>
-      </c>
-    </row>
-    <row r="183" spans="3:4">
-      <c r="C183">
-        <v>1388.7036000000001</v>
-      </c>
-    </row>
-    <row r="184" spans="3:4">
-      <c r="C184">
-        <v>1393.6958</v>
-      </c>
-    </row>
-    <row r="185" spans="3:4">
-      <c r="C185">
-        <v>1394.2116000000001</v>
-      </c>
-    </row>
-    <row r="186" spans="3:4">
-      <c r="C186">
-        <v>1395.2012</v>
-      </c>
-    </row>
-    <row r="187" spans="3:4">
-      <c r="C187">
-        <v>1407.7113999999999</v>
-      </c>
-    </row>
-    <row r="188" spans="3:4">
-      <c r="C188">
-        <v>1407.7227</v>
-      </c>
-    </row>
-    <row r="189" spans="3:4">
-      <c r="C189">
-        <v>1408.7011</v>
-      </c>
-    </row>
-    <row r="190" spans="3:4">
-      <c r="C190" s="6">
-        <v>1423.7064</v>
-      </c>
-      <c r="D190" s="6"/>
-    </row>
-    <row r="191" spans="3:4">
-      <c r="C191" s="6">
-        <v>1437.722</v>
-      </c>
-      <c r="D191" s="6"/>
-    </row>
-    <row r="192" spans="3:4">
-      <c r="C192">
-        <v>1440.7217000000001</v>
-      </c>
-    </row>
-    <row r="193" spans="3:3">
-      <c r="C193">
-        <v>1451.2275</v>
-      </c>
-    </row>
-    <row r="194" spans="3:3">
-      <c r="C194">
-        <v>1452.7273</v>
-      </c>
-    </row>
-    <row r="195" spans="3:3">
-      <c r="C195">
-        <v>1458.7329</v>
-      </c>
-    </row>
-    <row r="196" spans="3:3">
-      <c r="C196">
-        <v>1464.7329</v>
-      </c>
-    </row>
-    <row r="197" spans="3:3">
-      <c r="C197">
-        <v>1465.7407000000001</v>
-      </c>
-    </row>
-    <row r="198" spans="3:3">
-      <c r="C198">
-        <v>1467.2406000000001</v>
-      </c>
-    </row>
-    <row r="199" spans="3:3">
-      <c r="C199">
-        <v>1472.7485999999999</v>
-      </c>
-    </row>
-    <row r="200" spans="3:3">
-      <c r="C200">
-        <v>1473.7382</v>
-      </c>
-    </row>
-    <row r="201" spans="3:3">
-      <c r="C201">
-        <v>1480.7460000000001</v>
-      </c>
-    </row>
-    <row r="202" spans="3:3">
-      <c r="C202">
-        <v>1481.2562</v>
-      </c>
-    </row>
-    <row r="203" spans="3:3">
-      <c r="C203">
-        <v>1481.7482</v>
-      </c>
-    </row>
-    <row r="204" spans="3:3">
-      <c r="C204">
-        <v>1482.2457999999999</v>
-      </c>
-    </row>
-    <row r="205" spans="3:3">
-      <c r="C205">
-        <v>1489.2537</v>
-      </c>
-    </row>
-    <row r="206" spans="3:3">
-      <c r="C206">
-        <v>1497.2511</v>
-      </c>
-    </row>
-    <row r="207" spans="3:3">
-      <c r="C207">
-        <v>1502.7535</v>
-      </c>
-    </row>
-    <row r="208" spans="3:3">
-      <c r="C208">
-        <v>1510.7747999999999</v>
-      </c>
-    </row>
-    <row r="209" spans="3:3">
-      <c r="C209">
-        <v>1511.7588000000001</v>
-      </c>
-    </row>
-    <row r="210" spans="3:3">
-      <c r="C210">
-        <v>1516.259</v>
-      </c>
-    </row>
-    <row r="211" spans="3:3">
-      <c r="C211">
-        <v>1517.7588000000001</v>
-      </c>
-    </row>
-    <row r="212" spans="3:3">
-      <c r="C212">
-        <v>1531.2642000000001</v>
-      </c>
-    </row>
-    <row r="213" spans="3:3">
-      <c r="C213">
-        <v>1532.7641000000001</v>
-      </c>
-    </row>
-    <row r="214" spans="3:3">
-      <c r="C214">
-        <v>1540.7853</v>
-      </c>
-    </row>
-    <row r="215" spans="3:3">
-      <c r="C215">
-        <v>1545.7774999999999</v>
-      </c>
-    </row>
-    <row r="216" spans="3:3">
-      <c r="C216">
-        <v>1546.2695000000001</v>
-      </c>
-    </row>
-    <row r="217" spans="3:3">
-      <c r="C217">
-        <v>1552.7853</v>
-      </c>
-    </row>
-    <row r="218" spans="3:3">
-      <c r="C218">
-        <v>1554.8009999999999</v>
-      </c>
-    </row>
-    <row r="219" spans="3:3">
-      <c r="C219">
-        <v>1560.7828</v>
-      </c>
-    </row>
-    <row r="220" spans="3:3">
-      <c r="C220">
-        <v>1561.2747999999999</v>
-      </c>
-    </row>
-    <row r="221" spans="3:3">
-      <c r="C221">
-        <v>1567.7906</v>
-      </c>
-    </row>
-    <row r="222" spans="3:3">
-      <c r="C222">
-        <v>1570.7959000000001</v>
-      </c>
-    </row>
-    <row r="223" spans="3:3">
-      <c r="C223">
-        <v>1574.7893999999999</v>
-      </c>
-    </row>
-    <row r="224" spans="3:3">
-      <c r="C224">
-        <v>1575.7881</v>
-      </c>
-    </row>
-    <row r="225" spans="3:3">
-      <c r="C225">
-        <v>1576.2982999999999</v>
-      </c>
-    </row>
-    <row r="226" spans="3:3">
-      <c r="C226">
-        <v>1582.7959000000001</v>
-      </c>
-    </row>
-    <row r="227" spans="3:3">
-      <c r="C227">
-        <v>1590.7934</v>
-      </c>
-    </row>
-    <row r="228" spans="3:3">
-      <c r="C228">
-        <v>1591.3036</v>
-      </c>
-    </row>
-    <row r="229" spans="3:3">
-      <c r="C229">
-        <v>1595.8275000000001</v>
-      </c>
-    </row>
-    <row r="230" spans="3:3">
-      <c r="C230">
-        <v>1597.7955999999999</v>
-      </c>
-    </row>
-    <row r="231" spans="3:3">
-      <c r="C231">
-        <v>1605.7986000000001</v>
-      </c>
-    </row>
-    <row r="232" spans="3:3">
-      <c r="C232">
-        <v>1607.8275000000001</v>
-      </c>
-    </row>
-    <row r="233" spans="3:3">
-      <c r="C233">
-        <v>1611.8225</v>
-      </c>
-    </row>
-    <row r="234" spans="3:3">
-      <c r="C234">
-        <v>1625.3167000000001</v>
-      </c>
-    </row>
-    <row r="235" spans="3:3">
-      <c r="C235">
-        <v>1627.8061</v>
-      </c>
-    </row>
-    <row r="236" spans="3:3">
-      <c r="C236">
-        <v>1640.3219999999999</v>
-      </c>
-    </row>
-    <row r="237" spans="3:3">
-      <c r="C237">
-        <v>1654.8352</v>
-      </c>
-    </row>
-    <row r="238" spans="3:3">
-      <c r="C238">
-        <v>1655.3271999999999</v>
-      </c>
-    </row>
-    <row r="239" spans="3:3">
-      <c r="C239">
-        <v>1668.8326999999999</v>
-      </c>
-    </row>
-    <row r="240" spans="3:3">
-      <c r="C240">
-        <v>1669.8405</v>
-      </c>
-    </row>
-    <row r="241" spans="3:3">
-      <c r="C241">
-        <v>1676.8483000000001</v>
-      </c>
-    </row>
-    <row r="242" spans="3:3">
-      <c r="C242">
-        <v>1684.8458000000001</v>
-      </c>
-    </row>
-    <row r="243" spans="3:3">
-      <c r="C243">
-        <v>1685.848</v>
-      </c>
-    </row>
-    <row r="244" spans="3:3">
-      <c r="C244">
-        <v>1699.8511000000001</v>
-      </c>
-    </row>
-    <row r="245" spans="3:3">
-      <c r="C245">
-        <v>1699.8635999999999</v>
-      </c>
-    </row>
-    <row r="246" spans="3:3">
-      <c r="C246">
-        <v>1714.8744999999999</v>
-      </c>
-    </row>
-    <row r="247" spans="3:3">
-      <c r="C247">
-        <v>1715.8586</v>
-      </c>
-    </row>
-    <row r="248" spans="3:3">
-      <c r="C248">
-        <v>1726.8744999999999</v>
-      </c>
-    </row>
-    <row r="249" spans="3:3">
-      <c r="C249">
-        <v>1727.8697999999999</v>
-      </c>
-    </row>
-    <row r="250" spans="3:3">
-      <c r="C250">
-        <v>1728.8902</v>
-      </c>
-    </row>
-    <row r="251" spans="3:3">
-      <c r="C251">
-        <v>1741.8853999999999</v>
-      </c>
-    </row>
-    <row r="252" spans="3:3">
-      <c r="C252">
-        <v>1744.8851</v>
-      </c>
-    </row>
-    <row r="253" spans="3:3">
-      <c r="C253">
-        <v>1756.8851</v>
-      </c>
-    </row>
-    <row r="254" spans="3:3">
-      <c r="C254">
-        <v>1758.9007999999999</v>
-      </c>
-    </row>
-    <row r="255" spans="3:3">
-      <c r="C255">
-        <v>1763.8929000000001</v>
-      </c>
-    </row>
-    <row r="256" spans="3:3">
-      <c r="C256">
-        <v>1774.8957</v>
-      </c>
-    </row>
-    <row r="257" spans="3:3">
-      <c r="C257">
-        <v>1778.8982000000001</v>
-      </c>
-    </row>
-    <row r="258" spans="3:3">
-      <c r="C258">
-        <v>1785.9117000000001</v>
-      </c>
-    </row>
-    <row r="259" spans="3:3">
-      <c r="C259">
-        <v>1793.9034999999999</v>
-      </c>
-    </row>
-    <row r="260" spans="3:3">
-      <c r="C260">
-        <v>1799.9273000000001</v>
-      </c>
-    </row>
-    <row r="261" spans="3:3">
-      <c r="C261">
-        <v>1801.8952999999999</v>
-      </c>
-    </row>
-    <row r="262" spans="3:3">
-      <c r="C262">
-        <v>1815.9222</v>
-      </c>
-    </row>
-    <row r="263" spans="3:3">
-      <c r="C263">
-        <v>1831.9059</v>
-      </c>
-    </row>
-    <row r="264" spans="3:3">
-      <c r="C264">
-        <v>1842.9219000000001</v>
-      </c>
-    </row>
-    <row r="265" spans="3:3">
-      <c r="C265">
-        <v>1870.9644000000001</v>
-      </c>
-    </row>
-    <row r="266" spans="3:3">
-      <c r="C266">
-        <v>1872.9324999999999</v>
-      </c>
-    </row>
-    <row r="267" spans="3:3">
-      <c r="C267">
-        <v>1886.9481000000001</v>
-      </c>
-    </row>
-    <row r="268" spans="3:3">
-      <c r="C268">
-        <v>1889.9477999999999</v>
-      </c>
-    </row>
-    <row r="269" spans="3:3">
-      <c r="C269">
-        <v>1901.9590000000001</v>
-      </c>
-    </row>
-    <row r="270" spans="3:3">
-      <c r="C270">
-        <v>1913.9590000000001</v>
-      </c>
-    </row>
-    <row r="271" spans="3:3">
-      <c r="C271">
-        <v>1915.9747</v>
-      </c>
-    </row>
-    <row r="272" spans="3:3">
-      <c r="C272">
-        <v>1918.9743000000001</v>
-      </c>
-    </row>
-    <row r="273" spans="3:3">
-      <c r="C273">
-        <v>1930.9743000000001</v>
-      </c>
-    </row>
-    <row r="274" spans="3:3">
-      <c r="C274">
-        <v>1931.9695999999999</v>
-      </c>
-    </row>
-    <row r="275" spans="3:3">
-      <c r="C275">
-        <v>1932.99</v>
-      </c>
-    </row>
-    <row r="276" spans="3:3">
-      <c r="C276">
-        <v>1944.99</v>
-      </c>
-    </row>
-    <row r="277" spans="3:3">
-      <c r="C277">
-        <v>1945.9852000000001</v>
-      </c>
-    </row>
-    <row r="278" spans="3:3">
-      <c r="C278">
-        <v>1948.9848999999999</v>
-      </c>
-    </row>
-    <row r="279" spans="3:3">
-      <c r="C279">
-        <v>1960.0009</v>
-      </c>
-    </row>
-    <row r="280" spans="3:3">
-      <c r="C280">
-        <v>1960.9848999999999</v>
-      </c>
-    </row>
-    <row r="281" spans="3:3">
-      <c r="C281">
-        <v>1961.9801</v>
-      </c>
-    </row>
-    <row r="282" spans="3:3">
-      <c r="C282">
-        <v>1963.0005000000001</v>
-      </c>
-    </row>
-    <row r="283" spans="3:3">
-      <c r="C283">
-        <v>1990.0114000000001</v>
+      <c r="D11" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -9636,7 +8396,7 @@
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1:D1048576">
+  <conditionalFormatting sqref="B2:B3 C1:D1 C4:D1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9714,23 +8474,23 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B11" t="s">
         <v>270</v>
-      </c>
-      <c r="B11" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" t="s">
         <v>259</v>
-      </c>
-      <c r="B12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B14" t="s">
         <v>208</v>
@@ -9816,7 +8576,7 @@
         <v>220</v>
       </c>
       <c r="G3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H3" t="s">
         <v>235</v>
@@ -10006,7 +8766,7 @@
         <v>154</v>
       </c>
       <c r="E18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F18" t="s">
         <v>156</v>
@@ -10017,7 +8777,7 @@
         <v>155</v>
       </c>
       <c r="E19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -10033,51 +8793,51 @@
         <v>245</v>
       </c>
       <c r="E21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
+        <v>254</v>
+      </c>
+      <c r="B23" t="s">
         <v>255</v>
       </c>
-      <c r="B23" t="s">
-        <v>256</v>
-      </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="B24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E24" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="B25" t="s">
+        <v>257</v>
+      </c>
+      <c r="D25" t="s">
         <v>258</v>
       </c>
-      <c r="D25" t="s">
-        <v>259</v>
-      </c>
       <c r="E25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="D26" t="s">
+        <v>262</v>
+      </c>
+      <c r="E26" t="s">
         <v>263</v>
-      </c>
-      <c r="E26" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -10085,57 +8845,57 @@
         <v>153</v>
       </c>
       <c r="E27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="B29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -10444,31 +9204,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" t="s">
         <v>284</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>285</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>286</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>287</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G1" t="s">
         <v>288</v>
       </c>
-      <c r="F1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>289</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>290</v>
-      </c>
-      <c r="I1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -10494,10 +9254,10 @@
         <v>17392</v>
       </c>
       <c r="H2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I2" t="s">
         <v>292</v>
-      </c>
-      <c r="I2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -10523,10 +9283,10 @@
         <v>17499</v>
       </c>
       <c r="H3" t="s">
+        <v>293</v>
+      </c>
+      <c r="I3" t="s">
         <v>294</v>
-      </c>
-      <c r="I3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -10552,10 +9312,10 @@
         <v>17537</v>
       </c>
       <c r="H4" t="s">
+        <v>295</v>
+      </c>
+      <c r="I4" t="s">
         <v>296</v>
-      </c>
-      <c r="I4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -10581,10 +9341,10 @@
         <v>17649</v>
       </c>
       <c r="H5" t="s">
+        <v>297</v>
+      </c>
+      <c r="I5" t="s">
         <v>298</v>
-      </c>
-      <c r="I5" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -10610,10 +9370,10 @@
         <v>17720</v>
       </c>
       <c r="H6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I6" t="s">
         <v>300</v>
-      </c>
-      <c r="I6" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -10639,10 +9399,10 @@
         <v>17770</v>
       </c>
       <c r="H7" t="s">
+        <v>301</v>
+      </c>
+      <c r="I7" t="s">
         <v>302</v>
-      </c>
-      <c r="I7" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -10668,10 +9428,10 @@
         <v>17882</v>
       </c>
       <c r="H8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I8" t="s">
         <v>304</v>
-      </c>
-      <c r="I8" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -10697,10 +9457,10 @@
         <v>17954</v>
       </c>
       <c r="H9" t="s">
+        <v>305</v>
+      </c>
+      <c r="I9" t="s">
         <v>306</v>
-      </c>
-      <c r="I9" t="s">
-        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -10716,7 +9476,7 @@
   <sheetData>
     <row r="1" spans="1:287">
       <c r="A1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B1">
         <v>189.1121</v>
@@ -11565,16 +10325,16 @@
         <v>1990.0114000000001</v>
       </c>
       <c r="JX1" t="s">
+        <v>279</v>
+      </c>
+      <c r="JY1" t="s">
         <v>280</v>
       </c>
-      <c r="JY1" t="s">
+      <c r="JZ1" t="s">
         <v>281</v>
       </c>
-      <c r="JZ1" t="s">
+      <c r="KA1" t="s">
         <v>282</v>
-      </c>
-      <c r="KA1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:287">
@@ -18456,10 +17216,10 @@
         <v>17770</v>
       </c>
       <c r="H10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I10" t="s">
         <v>302</v>
-      </c>
-      <c r="I10" t="s">
-        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -18477,15 +17237,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100B01D25D17823C344A9D69518AF56DC62" ma:contentTypeVersion="6" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f29605d1c82d3d43c74cd3efc573dd15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f82b70a8-9591-478e-a6d5-bf315b83c485" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d7d0483a01e3419b531383906934819f" ns3:_="">
     <xsd:import namespace="f82b70a8-9591-478e-a6d5-bf315b83c485"/>
@@ -18641,6 +17392,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFEF422C-B8D3-4F6C-950A-A4DFD4067B7B}">
   <ds:schemaRefs>
@@ -18658,14 +17418,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80E8E46-C8F1-4EA0-9D75-58D6A3F6209E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3840DE93-E5DB-49F7-A595-E7AEB960EE63}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18681,4 +17433,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80E8E46-C8F1-4EA0-9D75-58D6A3F6209E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>